--- a/Plotting/Results_excels/production_shares_ammonia_Scope1-2.xlsx
+++ b/Plotting/Results_excels/production_shares_ammonia_Scope1-2.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,13 +483,6 @@
       </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Iteration_3</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -542,26 +535,11 @@
           <t>2050</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Conventional</t>
+          <t>Conventional (fossil)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -574,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1184000.000000019</v>
+        <v>1183999.999999978</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -583,28 +561,19 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1183999.999999995</v>
+        <v>1183999.999999916</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1184000.00000003</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Carbon Capture</t>
+          <t>Conventional (fossil) with CC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -634,15 +603,6 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -660,10 +620,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1.80409352167688e-08</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1181739.221044932</v>
+        <v>1181741.07602481</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -672,18 +632,9 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1181734.682806534</v>
+        <v>1181738.141773292</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1181739.385345381</v>
-      </c>
-      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -703,13 +654,13 @@
         <v>1180474.661760693</v>
       </c>
       <c r="E7" t="n">
-        <v>1.979831757394561e-10</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1183984.965423797</v>
+        <v>1183999.999999998</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -718,16 +669,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1183896.153265644</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1183897.260867802</v>
+        <v>1184000.000000006</v>
       </c>
     </row>
     <row r="8">
@@ -763,15 +705,6 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -806,15 +739,6 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -849,15 +773,6 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -892,15 +807,6 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -935,15 +841,6 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -978,15 +875,6 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1021,15 +909,6 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1064,22 +943,12 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
